--- a/test_informe_final.xlsx
+++ b/test_informe_final.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,14 +34,6 @@
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="14"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
       <color theme="1"/>
       <sz val="14"/>
       <scheme val="minor"/>
@@ -71,7 +63,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -151,18 +143,69 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -172,99 +215,72 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -608,361 +624,294 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J199"/>
+  <dimension ref="A1:J299"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>INFORME DE TAREAS POR CADA UNA DE LA ACTIVIDADES DEL CONTRATO DE PRESTACIÓN DE SERVICIOS</t>
         </is>
       </c>
-      <c r="B1" s="27" t="n"/>
-      <c r="C1" s="27" t="n"/>
-      <c r="D1" s="27" t="n"/>
-      <c r="E1" s="27" t="n"/>
-      <c r="F1" s="27" t="n"/>
-      <c r="G1" s="27" t="n"/>
-      <c r="H1" s="27" t="n"/>
-      <c r="I1" s="27" t="n"/>
-      <c r="J1" s="28" t="n"/>
+      <c r="B1" s="32" t="n"/>
+      <c r="C1" s="32" t="n"/>
+      <c r="D1" s="32" t="n"/>
+      <c r="E1" s="32" t="n"/>
+      <c r="F1" s="32" t="n"/>
+      <c r="G1" s="32" t="n"/>
+      <c r="H1" s="32" t="n"/>
+      <c r="I1" s="32" t="n"/>
+      <c r="J1" s="33" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>No. CONVENIO O CONTRATO:</t>
         </is>
       </c>
-      <c r="B2" s="28" t="n"/>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="33" t="n"/>
+      <c r="C2" s="21" t="inlineStr">
         <is>
           <t>2024-FINAL-001</t>
         </is>
       </c>
-      <c r="D2" s="27" t="n"/>
-      <c r="E2" s="27" t="n"/>
-      <c r="F2" s="27" t="n"/>
-      <c r="G2" s="27" t="n"/>
-      <c r="H2" s="27" t="n"/>
-      <c r="I2" s="27" t="n"/>
-      <c r="J2" s="28" t="n"/>
+      <c r="D2" s="32" t="n"/>
+      <c r="E2" s="32" t="n"/>
+      <c r="F2" s="32" t="n"/>
+      <c r="G2" s="32" t="n"/>
+      <c r="H2" s="32" t="n"/>
+      <c r="I2" s="32" t="n"/>
+      <c r="J2" s="33" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>OBJETO DEL CONTRATO:</t>
         </is>
       </c>
-      <c r="B3" s="28" t="n"/>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="B3" s="33" t="n"/>
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>CONTRATO DE PRUEBA FINAL</t>
         </is>
       </c>
-      <c r="D3" s="27" t="n"/>
-      <c r="E3" s="27" t="n"/>
-      <c r="F3" s="27" t="n"/>
-      <c r="G3" s="27" t="n"/>
-      <c r="H3" s="27" t="n"/>
-      <c r="I3" s="27" t="n"/>
-      <c r="J3" s="28" t="n"/>
+      <c r="D3" s="32" t="n"/>
+      <c r="E3" s="32" t="n"/>
+      <c r="F3" s="32" t="n"/>
+      <c r="G3" s="32" t="n"/>
+      <c r="H3" s="32" t="n"/>
+      <c r="I3" s="32" t="n"/>
+      <c r="J3" s="33" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>NOMBRE DEL CONTRATISTA:</t>
         </is>
       </c>
-      <c r="B4" s="28" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>JUAN PRUEBA</t>
         </is>
       </c>
-      <c r="D4" s="27" t="n"/>
-      <c r="E4" s="27" t="n"/>
-      <c r="F4" s="27" t="n"/>
-      <c r="G4" s="27" t="n"/>
-      <c r="H4" s="27" t="n"/>
-      <c r="I4" s="27" t="n"/>
-      <c r="J4" s="28" t="n"/>
+      <c r="D4" s="32" t="n"/>
+      <c r="E4" s="32" t="n"/>
+      <c r="F4" s="32" t="n"/>
+      <c r="G4" s="32" t="n"/>
+      <c r="H4" s="32" t="n"/>
+      <c r="I4" s="32" t="n"/>
+      <c r="J4" s="33" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>No DE IDENTIFICACIÓN:</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n"/>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>999999</t>
         </is>
       </c>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="27" t="n"/>
-      <c r="F5" s="27" t="n"/>
-      <c r="G5" s="27" t="n"/>
-      <c r="H5" s="27" t="n"/>
-      <c r="I5" s="27" t="n"/>
-      <c r="J5" s="28" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="32" t="n"/>
+      <c r="H5" s="32" t="n"/>
+      <c r="I5" s="32" t="n"/>
+      <c r="J5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>FECHA DE ACTIVIDADES:</t>
         </is>
       </c>
-      <c r="B6" s="28" t="n"/>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>13/02/2026 al 13/02/2026</t>
-        </is>
-      </c>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="27" t="n"/>
-      <c r="G6" s="27" t="n"/>
-      <c r="H6" s="27" t="n"/>
-      <c r="I6" s="27" t="n"/>
-      <c r="J6" s="28" t="n"/>
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>16/02/2026 al 16/02/2026</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="n"/>
+      <c r="E6" s="32" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="32" t="n"/>
+      <c r="H6" s="32" t="n"/>
+      <c r="I6" s="32" t="n"/>
+      <c r="J6" s="33" t="n"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>TIPO DE ACTIVIDA</t>
-        </is>
-      </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="28" t="n"/>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>TIPO DE ACTIVIDAD</t>
+        </is>
+      </c>
+      <c r="B7" s="32" t="n"/>
+      <c r="C7" s="32" t="n"/>
+      <c r="D7" s="32" t="n"/>
+      <c r="E7" s="32" t="n"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="33" t="n"/>
+      <c r="H7" s="35" t="inlineStr">
         <is>
           <t>CANTIDAD</t>
         </is>
       </c>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="28" t="n"/>
-    </row>
-    <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
-        <is>
-          <t>RESUMEN DE ACTIVIDADES REALIZADAS:</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="27" t="n"/>
-      <c r="G8" s="27" t="n"/>
-      <c r="H8" s="28" t="n"/>
-    </row>
-    <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Coadyuvar con las actividades del proceso del Sistema de Gestión de Calidad.</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>DESCRIPCIÓN DE LA ACTIVIDAD</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="n"/>
-      <c r="C10" s="31" t="n"/>
-      <c r="D10" s="31" t="n"/>
-      <c r="E10" s="31" t="n"/>
-      <c r="F10" s="32" t="n">
-        <v>48</v>
-      </c>
-      <c r="G10" s="31" t="n"/>
-      <c r="H10" s="31" t="n"/>
-      <c r="I10" s="33" t="inlineStr">
-        <is>
-          <t>CONTEO</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="I7" s="32" t="n"/>
+      <c r="J7" s="33" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Mantenimiento</t>
         </is>
       </c>
-      <c r="B11" s="31" t="n"/>
-      <c r="C11" s="31" t="n"/>
-      <c r="D11" s="31" t="n"/>
-      <c r="E11" s="31" t="n"/>
-      <c r="F11" s="31" t="n"/>
-      <c r="G11" s="31" t="n"/>
-      <c r="H11" s="31" t="n"/>
-      <c r="I11" s="31" t="n">
+      <c r="B8" s="32" t="n"/>
+      <c r="C8" s="32" t="n"/>
+      <c r="D8" s="32" t="n"/>
+      <c r="E8" s="32" t="n"/>
+      <c r="F8" s="32" t="n"/>
+      <c r="G8" s="33" t="n"/>
+      <c r="H8" s="36" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="I8" s="37" t="n"/>
+      <c r="J8" s="38" t="n"/>
+    </row>
+    <row r="9" ht="25.5" customHeight="1">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t>Soporte Técnico</t>
         </is>
       </c>
-      <c r="B12" s="31" t="n"/>
-      <c r="C12" s="31" t="n"/>
-      <c r="D12" s="31" t="n"/>
-      <c r="E12" s="31" t="n"/>
-      <c r="F12" s="31" t="n"/>
-      <c r="G12" s="31" t="n"/>
-      <c r="H12" s="31" t="n"/>
-      <c r="I12" s="31" t="n">
+      <c r="B9" s="32" t="n"/>
+      <c r="C9" s="32" t="n"/>
+      <c r="D9" s="32" t="n"/>
+      <c r="E9" s="32" t="n"/>
+      <c r="F9" s="32" t="n"/>
+      <c r="G9" s="33" t="n"/>
+      <c r="H9" s="40" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="I9" s="37" t="n"/>
+      <c r="J9" s="38" t="n"/>
+    </row>
+    <row r="10" ht="25.5" customHeight="1">
+      <c r="A10" s="41" t="inlineStr">
         <is>
           <t>Capacitación</t>
         </is>
       </c>
-      <c r="B13" s="31" t="n"/>
-      <c r="C13" s="31" t="n"/>
-      <c r="D13" s="31" t="n"/>
-      <c r="E13" s="31" t="n"/>
-      <c r="F13" s="31" t="n"/>
-      <c r="G13" s="31" t="n"/>
-      <c r="H13" s="31" t="n"/>
-      <c r="I13" s="31" t="n">
+      <c r="B10" s="32" t="n"/>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="32" t="n"/>
+      <c r="E10" s="32" t="n"/>
+      <c r="F10" s="32" t="n"/>
+      <c r="G10" s="33" t="n"/>
+      <c r="H10" s="42" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="I10" s="37" t="n"/>
+      <c r="J10" s="38" t="n"/>
+    </row>
+    <row r="11" ht="39" customHeight="1">
+      <c r="A11" s="43" t="inlineStr">
         <is>
           <t>TOTAL GENERAL DE ACTIVIDADES:</t>
         </is>
       </c>
-      <c r="B14" s="31" t="n"/>
-      <c r="C14" s="31" t="n"/>
-      <c r="D14" s="31" t="n"/>
-      <c r="E14" s="31" t="n"/>
-      <c r="F14" s="31" t="n"/>
-      <c r="G14" s="31" t="n"/>
-      <c r="H14" s="31" t="n"/>
-      <c r="I14" s="33" t="n">
+      <c r="B11" s="32" t="n"/>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="32" t="n"/>
+      <c r="E11" s="32" t="n"/>
+      <c r="F11" s="32" t="n"/>
+      <c r="G11" s="33" t="n"/>
+      <c r="H11" s="44" t="n">
         <v>6</v>
       </c>
-      <c r="J14" s="11" t="n"/>
-    </row>
-    <row r="15" ht="25.5" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fecha de informe:  </t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>15 Octubre 2025</t>
-        </is>
-      </c>
-      <c r="H15" s="14" t="n"/>
-      <c r="I15" s="14" t="n"/>
-      <c r="J15" s="14" t="n"/>
-    </row>
-    <row r="16" ht="25.5" customHeight="1">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="I11" s="37" t="n"/>
+      <c r="J11" s="38" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Vo Bo:</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Mario Alfonso Henao Lopez</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="38.25" customHeight="1">
+      <c r="A13" s="45" t="inlineStr">
         <is>
           <t>Fecha de informe:</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Febrero de 2026</t>
         </is>
       </c>
-      <c r="C16" s="27" t="n"/>
-      <c r="D16" s="27" t="n"/>
-      <c r="E16" s="27" t="n"/>
-      <c r="F16" s="27" t="n"/>
-      <c r="G16" s="27" t="n"/>
-      <c r="H16" s="28" t="n"/>
-      <c r="I16" s="17" t="n"/>
-      <c r="J16" s="17" t="n"/>
-    </row>
-    <row r="17" ht="39" customHeight="1">
-      <c r="A17" s="36" t="inlineStr">
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="32" t="n"/>
+      <c r="E13" s="32" t="n"/>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="33" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="46" t="inlineStr">
         <is>
           <t>Elaborado por:</t>
         </is>
       </c>
-      <c r="B17" s="37" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>JUAN PRUEBA</t>
         </is>
       </c>
-      <c r="C17" s="27" t="n"/>
-      <c r="D17" s="27" t="n"/>
-      <c r="E17" s="27" t="n"/>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="27" t="n"/>
-      <c r="H17" s="28" t="n"/>
-      <c r="I17" s="22" t="n"/>
-      <c r="J17" s="22" t="n"/>
-    </row>
+    </row>
+    <row r="16">
+      <c r="A16" s="46" t="inlineStr">
+        <is>
+          <t>CONTRATISTA:</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
-        <is>
-          <t>CONTRATISTA:</t>
-        </is>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>Mario Alfonso Henao Lopez</t>
-        </is>
-      </c>
-      <c r="C18" s="27" t="n"/>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="27" t="n"/>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="27" t="n"/>
-      <c r="H18" s="28" t="n"/>
-      <c r="I18" s="24" t="n"/>
-      <c r="J18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="38.25" customHeight="1">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A18" s="46" t="inlineStr">
         <is>
           <t>Vo.Bo:</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>SUPERVISOR PRUEBA</t>
         </is>
       </c>
-      <c r="C19" s="27" t="n"/>
-      <c r="D19" s="27" t="n"/>
-      <c r="E19" s="27" t="n"/>
-      <c r="F19" s="27" t="n"/>
-      <c r="G19" s="27" t="n"/>
-      <c r="H19" s="28" t="n"/>
-      <c r="I19" s="26" t="n"/>
-      <c r="J19" s="26" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="38" t="inlineStr">
+    </row>
+    <row r="19">
+      <c r="A19" s="46" t="inlineStr">
         <is>
           <t>SUPERVISOR:</t>
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21"/>
     <row r="22"/>
     <row r="23"/>
@@ -1142,31 +1091,134 @@
     <row r="197"/>
     <row r="198"/>
     <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
+    <row r="226"/>
+    <row r="227"/>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266"/>
+    <row r="267"/>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="26">
     <mergeCell ref="C3:J3"/>
+    <mergeCell ref="A8:G8"/>
     <mergeCell ref="C6:J6"/>
-    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="B13:G13"/>
     <mergeCell ref="C5:J5"/>
-    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="H11:J11"/>
     <mergeCell ref="A6:B6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="A10:G10"/>
     <mergeCell ref="C4:J4"/>
-    <mergeCell ref="F7:J7"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="A9:G9"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="B15:G15"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="C2:J2"/>
+    <mergeCell ref="H8:J8"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C2:J2"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A7:G7"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="B18:G18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test_informe_final.xlsx
+++ b/test_informe_final.xlsx
@@ -624,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J299"/>
+  <dimension ref="A1:K300"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -836,16 +836,8 @@
       <c r="J11" s="38" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Vo Bo:</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Mario Alfonso Henao Lopez</t>
-        </is>
-      </c>
+      <c r="A12" s="3" t="n"/>
+      <c r="B12" s="15" t="n"/>
       <c r="G12" s="7" t="n"/>
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="7" t="n"/>
@@ -1191,6 +1183,7 @@
     <row r="297"/>
     <row r="298"/>
     <row r="299"/>
+    <row r="300"/>
   </sheetData>
   <mergeCells count="26">
     <mergeCell ref="C3:J3"/>
